--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-PLN-02_tedarik_guvence_plani_ve_riskli_tedarikci_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-PLN-02_tedarik_guvence_plani_ve_riskli_tedarikci_listesi.xlsx
@@ -948,7 +948,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Tedarik Güvence Planı ve Riskli Tedarikçi Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Tedarik teminat hesabına negatif stok, transit ve geçersiz tüketim denetimleri eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b58af7c2f484a6d"/>
   <x:tableParts count="1">
@@ -1314,7 +1315,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Tedarik Güvence Planı ve Riskli Tedarikçi Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Tedarik teminat hesabına negatif stok, transit ve geçersiz tüketim denetimleri eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b2bc94b96404e9c"/>
   <x:tableParts count="1">
@@ -1662,7 +1664,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Tedarik Güvence Planı ve Riskli Tedarikçi Listesi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Tedarik teminat hesabına negatif stok, transit ve geçersiz tüketim denetimleri eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb4c598ee7c04322"/>
   <x:tableParts count="1">
